--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joaobiosmac/Desktop/Trabalhos &amp; Repositórios/Artigos em Andamento/Revisao Esli/Freshwater Biology/Revisao_Esli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1FA77A-8556-0547-B4DB-22F2733E744A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1216C01-B747-6E46-B6CA-84680159D651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="600" windowWidth="26200" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$126</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="261">
   <si>
     <t>title</t>
   </si>
@@ -797,6 +797,15 @@
   </si>
   <si>
     <t>status_crust</t>
+  </si>
+  <si>
+    <t>Predation on a cave fish by the freshwater crab Avotrichodactylus bidens (Bott, 1969) (Brachyura, Trichodactylidae) in a Mexican sulfur cave</t>
+  </si>
+  <si>
+    <t>Cave/ Subterranean Freshwater Systems</t>
+  </si>
+  <si>
+    <t>Trichodactylidae</t>
   </si>
 </sst>
 </file>
@@ -845,7 +854,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="11" width="40.33203125" customWidth="1"/>
@@ -1998,60 +2009,60 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>258</v>
       </c>
       <c r="B25">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" t="s">
-        <v>252</v>
-      </c>
-      <c r="I25" t="s">
-        <v>252</v>
-      </c>
-      <c r="J25" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26">
         <v>2010</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="H26" t="s">
         <v>252</v>
@@ -2063,30 +2074,30 @@
         <v>12</v>
       </c>
       <c r="K26" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B27">
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H27" t="s">
         <v>252</v>
@@ -2103,10 +2114,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B28">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C28" t="s">
         <v>47</v>
@@ -2118,7 +2129,7 @@
         <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -2133,30 +2144,30 @@
         <v>12</v>
       </c>
       <c r="K28" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B29">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
         <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H29" t="s">
         <v>252</v>
@@ -2173,13 +2184,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B30">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
         <v>86</v>
@@ -2208,25 +2219,25 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B31">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
         <v>252</v>
@@ -2238,36 +2249,36 @@
         <v>12</v>
       </c>
       <c r="K31" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B32">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s">
         <v>252</v>
       </c>
       <c r="I32" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J32" t="s">
         <v>12</v>
@@ -2278,22 +2289,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33">
         <v>2007</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -2302,7 +2313,7 @@
         <v>252</v>
       </c>
       <c r="I33" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J33" t="s">
         <v>12</v>
@@ -2313,31 +2324,31 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B34">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="H34" t="s">
         <v>252</v>
       </c>
       <c r="I34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J34" t="s">
         <v>12</v>
@@ -2348,31 +2359,31 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B35">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s">
+        <v>252</v>
+      </c>
+      <c r="I35" t="s">
         <v>254</v>
-      </c>
-      <c r="I35" t="s">
-        <v>252</v>
       </c>
       <c r="J35" t="s">
         <v>12</v>
@@ -2383,31 +2394,31 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B36">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="H36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J36" t="s">
         <v>12</v>
@@ -2418,60 +2429,60 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B37">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H37" t="s">
         <v>252</v>
       </c>
       <c r="I37" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J37" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K37" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B38">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="G38" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H38" t="s">
         <v>252</v>
@@ -2480,33 +2491,33 @@
         <v>252</v>
       </c>
       <c r="J38" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B39">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D39" t="s">
         <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s">
         <v>252</v>
@@ -2518,18 +2529,18 @@
         <v>12</v>
       </c>
       <c r="K39" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40">
         <v>2004</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
         <v>86</v>
@@ -2538,7 +2549,7 @@
         <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -2553,30 +2564,30 @@
         <v>12</v>
       </c>
       <c r="K40" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B41">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="H41" t="s">
         <v>252</v>
@@ -2588,74 +2599,74 @@
         <v>12</v>
       </c>
       <c r="K41" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B42">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C42" t="s">
         <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F42" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I42" t="s">
         <v>252</v>
       </c>
       <c r="J42" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K42" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B43">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F43" t="s">
         <v>72</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I43" t="s">
         <v>252</v>
       </c>
       <c r="J43" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="K43" t="s">
         <v>26</v>
@@ -2663,13 +2674,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B44">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
         <v>86</v>
@@ -2698,25 +2709,25 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B45">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
         <v>86</v>
       </c>
       <c r="E45" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
         <v>252</v>
@@ -2725,33 +2736,33 @@
         <v>252</v>
       </c>
       <c r="J45" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B46">
         <v>2000</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
         <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="H46" t="s">
         <v>252</v>
@@ -2768,13 +2779,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B47">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
         <v>86</v>
@@ -2783,7 +2794,7 @@
         <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -2803,101 +2814,101 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F48" t="s">
         <v>23</v>
       </c>
       <c r="G48" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
         <v>252</v>
       </c>
       <c r="I48" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J48" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K48" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B49">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
         <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s">
         <v>252</v>
       </c>
       <c r="I49" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J49" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="K49" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B50">
         <v>1996</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I50" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J50" t="s">
         <v>12</v>
@@ -2908,31 +2919,31 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B51">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
       </c>
       <c r="H51" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I51" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J51" t="s">
         <v>12</v>
@@ -2943,16 +2954,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B52">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C52" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E52" t="s">
         <v>36</v>
@@ -2967,7 +2978,7 @@
         <v>252</v>
       </c>
       <c r="I52" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J52" t="s">
         <v>12</v>
@@ -2978,16 +2989,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B53">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E53" t="s">
         <v>36</v>
@@ -3002,7 +3013,7 @@
         <v>252</v>
       </c>
       <c r="I53" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J53" t="s">
         <v>12</v>
@@ -3013,25 +3024,25 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B54">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="D54" t="s">
         <v>86</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F54" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="G54" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="H54" t="s">
         <v>252</v>
@@ -3048,31 +3059,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B55">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H55" t="s">
         <v>252</v>
       </c>
       <c r="I55" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J55" t="s">
         <v>12</v>
@@ -3083,31 +3094,31 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B56">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="C56" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
         <v>252</v>
       </c>
       <c r="I56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J56" t="s">
         <v>12</v>
@@ -3118,31 +3129,31 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B57">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E57" t="s">
         <v>36</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s">
         <v>252</v>
       </c>
       <c r="I57" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J57" t="s">
         <v>12</v>
@@ -3153,31 +3164,31 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B58">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D58" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
         <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>252</v>
+        <v>11</v>
+      </c>
+      <c r="H58" t="s">
+        <v>252</v>
+      </c>
+      <c r="I58" t="s">
+        <v>254</v>
       </c>
       <c r="J58" t="s">
         <v>12</v>
@@ -3188,31 +3199,31 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B59">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F59" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>254</v>
+        <v>70</v>
+      </c>
+      <c r="H59" t="s">
+        <v>252</v>
+      </c>
+      <c r="I59" t="s">
+        <v>252</v>
       </c>
       <c r="J59" t="s">
         <v>12</v>
@@ -3223,31 +3234,31 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B60">
-        <v>1967</v>
+        <v>1985</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
         <v>36</v>
       </c>
       <c r="F60" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>252</v>
+      <c r="H60" t="s">
+        <v>252</v>
+      </c>
+      <c r="I60" t="s">
+        <v>254</v>
       </c>
       <c r="J60" t="s">
         <v>12</v>
@@ -3258,101 +3269,101 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B61">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E61" t="s">
         <v>36</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I61" s="2" t="s">
+      <c r="H61" t="s">
+        <v>252</v>
+      </c>
+      <c r="I61" t="s">
         <v>252</v>
       </c>
       <c r="J61" t="s">
         <v>12</v>
       </c>
       <c r="K61" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B62">
-        <v>2025</v>
+        <v>1961</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I62" s="2" t="s">
+      <c r="H62" t="s">
+        <v>252</v>
+      </c>
+      <c r="I62" t="s">
         <v>252</v>
       </c>
       <c r="J62" t="s">
         <v>12</v>
       </c>
       <c r="K62" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B63">
         <v>2025</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="D63" t="s">
         <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="F63" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G63" t="s">
-        <v>83</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" t="s">
         <v>254</v>
+      </c>
+      <c r="I63" t="s">
+        <v>252</v>
       </c>
       <c r="J63" t="s">
         <v>12</v>
@@ -3363,31 +3374,31 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B64">
         <v>2025</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G64" t="s">
-        <v>23</v>
-      </c>
-      <c r="H64" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s">
+        <v>252</v>
+      </c>
+      <c r="I64" t="s">
         <v>254</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="J64" t="s">
         <v>12</v>
@@ -3398,31 +3409,31 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B65">
         <v>2025</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E65" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F65" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" t="s">
         <v>23</v>
       </c>
-      <c r="G65" t="s">
-        <v>11</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I65" s="2" t="s">
+      <c r="H65" t="s">
         <v>254</v>
+      </c>
+      <c r="I65" t="s">
+        <v>252</v>
       </c>
       <c r="J65" t="s">
         <v>12</v>
@@ -3433,31 +3444,31 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B66">
         <v>2025</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D66" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
-      </c>
-      <c r="H66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" t="s">
+        <v>252</v>
+      </c>
+      <c r="I66" t="s">
         <v>254</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="J66" t="s">
         <v>12</v>
@@ -3468,65 +3479,65 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B67">
         <v>2025</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="D67" t="s">
         <v>86</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="F67" t="s">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" t="s">
+        <v>254</v>
+      </c>
+      <c r="I67" t="s">
         <v>252</v>
       </c>
       <c r="J67" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K67" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B68">
         <v>2025</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="E68" t="s">
-        <v>200</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="G68" t="s">
         <v>30</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I68" s="2" t="s">
+      <c r="H68" t="s">
+        <v>252</v>
+      </c>
+      <c r="I68" t="s">
         <v>252</v>
       </c>
       <c r="J68" t="s">
@@ -3538,34 +3549,34 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B69">
         <v>2025</v>
       </c>
       <c r="C69" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F69" t="s">
         <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>254</v>
+        <v>30</v>
+      </c>
+      <c r="H69" t="s">
+        <v>252</v>
+      </c>
+      <c r="I69" t="s">
+        <v>252</v>
       </c>
       <c r="J69" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K69" t="s">
         <v>26</v>
@@ -3573,220 +3584,223 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B70">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C70" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E70" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>23</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>252</v>
+        <v>11</v>
+      </c>
+      <c r="H70" t="s">
+        <v>252</v>
+      </c>
+      <c r="I70" t="s">
+        <v>254</v>
       </c>
       <c r="J70" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="K70" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B71">
         <v>2023</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="D71" t="s">
         <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F71" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>83</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" t="s">
+        <v>252</v>
+      </c>
+      <c r="I71" t="s">
         <v>252</v>
       </c>
       <c r="J71" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="K71" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B72">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="F72" t="s">
-        <v>209</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s">
+        <v>252</v>
+      </c>
+      <c r="I72" t="s">
         <v>252</v>
       </c>
       <c r="J72" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B73">
         <v>2022</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="F73" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G73" t="s">
-        <v>83</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>254</v>
+        <v>30</v>
+      </c>
+      <c r="H73" t="s">
+        <v>252</v>
+      </c>
+      <c r="I73" t="s">
+        <v>252</v>
       </c>
       <c r="J73" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B74">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="F74" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>252</v>
+        <v>83</v>
+      </c>
+      <c r="H74" t="s">
+        <v>252</v>
+      </c>
+      <c r="I74" t="s">
+        <v>254</v>
       </c>
       <c r="J74" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B75">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="G75" t="s">
-        <v>51</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>254</v>
+        <v>30</v>
+      </c>
+      <c r="H75" t="s">
+        <v>252</v>
+      </c>
+      <c r="I75" t="s">
+        <v>252</v>
       </c>
       <c r="J75" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B76">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E76" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="F76" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="H76" t="s">
         <v>252</v>
@@ -3795,100 +3809,97 @@
         <v>254</v>
       </c>
       <c r="J76" t="s">
-        <v>12</v>
-      </c>
-      <c r="K76" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="B77">
         <v>2014</v>
       </c>
       <c r="C77" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
         <v>16</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F77" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H77" t="s">
         <v>252</v>
       </c>
       <c r="I77" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J77" t="s">
-        <v>253</v>
+        <v>12</v>
+      </c>
+      <c r="K77" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="B78">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D78" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>251</v>
       </c>
       <c r="G78" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="H78" t="s">
         <v>252</v>
       </c>
       <c r="I78" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J78" t="s">
-        <v>12</v>
-      </c>
-      <c r="K78" t="s">
-        <v>41</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B79">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D79" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E79" t="s">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="F79" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="G79" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s">
         <v>252</v>
@@ -3900,30 +3911,30 @@
         <v>12</v>
       </c>
       <c r="K79" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B80">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="D80" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F80" t="s">
-        <v>50</v>
+        <v>222</v>
       </c>
       <c r="G80" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="H80" t="s">
         <v>252</v>
@@ -3935,36 +3946,36 @@
         <v>12</v>
       </c>
       <c r="K80" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B81">
         <v>2011</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D81" t="s">
         <v>48</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="F81" t="s">
         <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="H81" t="s">
         <v>252</v>
       </c>
       <c r="I81" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J81" t="s">
         <v>12</v>
@@ -3975,25 +3986,25 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B82">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="D82" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E82" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="H82" t="s">
         <v>252</v>
@@ -4002,30 +4013,33 @@
         <v>252</v>
       </c>
       <c r="J82" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="K82" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B83">
         <v>2009</v>
       </c>
       <c r="C83" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
         <v>86</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="F83" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H83" t="s">
         <v>252</v>
@@ -4039,22 +4053,22 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B84">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="D84" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E84" t="s">
         <v>36</v>
       </c>
       <c r="F84" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -4066,30 +4080,27 @@
         <v>252</v>
       </c>
       <c r="J84" t="s">
-        <v>12</v>
-      </c>
-      <c r="K84" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B85">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C85" t="s">
-        <v>231</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E85" t="s">
         <v>36</v>
       </c>
       <c r="F85" t="s">
-        <v>228</v>
+        <v>50</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
@@ -4104,36 +4115,36 @@
         <v>12</v>
       </c>
       <c r="K85" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B86">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C86" t="s">
-        <v>124</v>
+        <v>231</v>
       </c>
       <c r="D86" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E86" t="s">
         <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="G86" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H86" t="s">
         <v>252</v>
       </c>
       <c r="I86" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J86" t="s">
         <v>12</v>
@@ -4144,25 +4155,25 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B87">
         <v>2002</v>
       </c>
       <c r="C87" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
         <v>48</v>
       </c>
       <c r="E87" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F87" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G87" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="H87" t="s">
         <v>252</v>
@@ -4179,31 +4190,31 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B88">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>234</v>
       </c>
       <c r="D88" t="s">
         <v>48</v>
       </c>
       <c r="E88" t="s">
-        <v>236</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G88" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H88" t="s">
         <v>252</v>
       </c>
       <c r="I88" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J88" t="s">
         <v>12</v>
@@ -4214,25 +4225,25 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B89">
         <v>2000</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E89" t="s">
-        <v>36</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="H89" t="s">
         <v>252</v>
@@ -4249,13 +4260,13 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B90">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="D90" t="s">
         <v>86</v>
@@ -4264,10 +4275,10 @@
         <v>36</v>
       </c>
       <c r="F90" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G90" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H90" t="s">
         <v>252</v>
@@ -4284,13 +4295,13 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B91">
         <v>1998</v>
       </c>
       <c r="C91" t="s">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="D91" t="s">
         <v>86</v>
@@ -4299,10 +4310,10 @@
         <v>36</v>
       </c>
       <c r="F91" t="s">
-        <v>241</v>
+        <v>40</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H91" t="s">
         <v>252</v>
@@ -4311,103 +4322,103 @@
         <v>252</v>
       </c>
       <c r="J91" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="K91" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B92">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C92" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="E92" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>44</v>
+        <v>241</v>
       </c>
       <c r="G92" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I92" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J92" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B93">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>243</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="F93" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="G93" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="H93" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I93" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J93" t="s">
-        <v>12</v>
-      </c>
-      <c r="K93" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B94">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E94" t="s">
-        <v>36</v>
+        <v>245</v>
       </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="H94" t="s">
         <v>252</v>
       </c>
       <c r="I94" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J94" t="s">
         <v>12</v>
@@ -4418,13 +4429,13 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B95">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="C95" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
         <v>86</v>
@@ -4433,7 +4444,7 @@
         <v>36</v>
       </c>
       <c r="F95" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
@@ -4448,33 +4459,33 @@
         <v>12</v>
       </c>
       <c r="K95" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B96">
-        <v>2025</v>
+        <v>1989</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D96" t="s">
         <v>86</v>
       </c>
       <c r="E96" t="s">
-        <v>248</v>
+        <v>36</v>
       </c>
       <c r="F96" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I96" t="s">
         <v>254</v>
@@ -4483,6 +4494,41 @@
         <v>12</v>
       </c>
       <c r="K96" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>255</v>
+      </c>
+      <c r="B97">
+        <v>2025</v>
+      </c>
+      <c r="C97" t="s">
+        <v>103</v>
+      </c>
+      <c r="D97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97" t="s">
+        <v>248</v>
+      </c>
+      <c r="F97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" t="s">
+        <v>254</v>
+      </c>
+      <c r="I97" t="s">
+        <v>254</v>
+      </c>
+      <c r="J97" t="s">
+        <v>12</v>
+      </c>
+      <c r="K97" t="s">
         <v>13</v>
       </c>
     </row>
